--- a/new original/_Lang_Chinese/Lang/CN/Game/Word.xlsx
+++ b/new original/_Lang_Chinese/Lang/CN/Game/Word.xlsx
@@ -35,7 +35,7 @@
     <t xml:space="preserve">100</t>
   </si>
   <si>
-    <t xml:space="preserve">EA 23.267</t>
+    <t xml:space="preserve">EA 23.282</t>
   </si>
   <si>
     <t xml:space="preserve">wrecked</t>
@@ -5237,7 +5237,7 @@
     <t xml:space="preserve">同伙,乌合之众,同党</t>
   </si>
   <si>
-    <t xml:space="preserve">团体,党,同伴</t>
+    <t xml:space="preserve">团体,团,同伴</t>
   </si>
   <si>
     <t xml:space="preserve">共同体,结社,秘密结社</t>
@@ -5291,7 +5291,7 @@
     <t xml:space="preserve">布道团,宣教团,僧侣团</t>
   </si>
   <si>
-    <t xml:space="preserve">阵,班,党</t>
+    <t xml:space="preserve">阵,班,队</t>
   </si>
   <si>
     <t xml:space="preserve">骑兵队,盗贼团,突击队,战队</t>

--- a/new original/_Lang_Chinese/Lang/CN/Game/Word.xlsx
+++ b/new original/_Lang_Chinese/Lang/CN/Game/Word.xlsx
@@ -35,7 +35,7 @@
     <t xml:space="preserve">100</t>
   </si>
   <si>
-    <t xml:space="preserve">EA 23.282</t>
+    <t xml:space="preserve">EA 23.287</t>
   </si>
   <si>
     <t xml:space="preserve">wrecked</t>

--- a/new original/_Lang_Chinese/Lang/CN/Game/Word.xlsx
+++ b/new original/_Lang_Chinese/Lang/CN/Game/Word.xlsx
@@ -35,7 +35,7 @@
     <t xml:space="preserve">100</t>
   </si>
   <si>
-    <t xml:space="preserve">EA 23.287</t>
+    <t xml:space="preserve">EA 23.295</t>
   </si>
   <si>
     <t xml:space="preserve">wrecked</t>

--- a/new original/_Lang_Chinese/Lang/CN/Game/Word.xlsx
+++ b/new original/_Lang_Chinese/Lang/CN/Game/Word.xlsx
@@ -35,7 +35,7 @@
     <t xml:space="preserve">100</t>
   </si>
   <si>
-    <t xml:space="preserve">EA 23.295</t>
+    <t xml:space="preserve">EA 23.287</t>
   </si>
   <si>
     <t xml:space="preserve">wrecked</t>
